--- a/output/daily_ratings/uk_ratings_2026-05-12.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-05-12.xlsx
@@ -942,34 +942,36 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Danger Alert</t>
+          <t>Thurso</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -998,28 +1000,30 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Candy Warhol (USA)</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>127</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Thurso</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>135</v>
-      </c>
-      <c r="K10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>65.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1056,30 +1060,30 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Candy Warhol (USA)</t>
+          <t>Some Nightmare (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K11" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>54.7</v>
+        <v>45.1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1087,7 +1091,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -1116,30 +1120,30 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Some Nightmare (IRE)</t>
+          <t>Dapperling (IRE)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>121</v>
       </c>
       <c r="K12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1147,7 +1151,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -1176,30 +1180,30 @@
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Dapperling (IRE)</t>
+          <t>Hidden Verse (IRE)</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>50.6</v>
+        <v>48.3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1207,7 +1211,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1236,30 +1240,30 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hidden Verse (IRE)</t>
+          <t>Under Curfew</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="K14" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>48.3</v>
+        <v>28.7</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1267,7 +1271,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -1296,30 +1300,30 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Under Curfew</t>
+          <t>The Feminine Urge (IRE)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>7.55</v>
       </c>
       <c r="M15" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>32</v>
+        <v>35.6</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1327,7 +1331,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1355,40 +1359,24 @@
       <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>7</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>The Feminine Urge (IRE)</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>131</v>
-      </c>
-      <c r="K16" t="n">
-        <v>64</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="M16" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="N16" t="n">
-        <v>35.6</v>
-      </c>
+          <t>Danger Alert</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1416,11 +1404,11 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Far From Fern</t>
+          <t>Noble Vow (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1430,20 +1418,22 @@
         <v>132</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>62.1</v>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1472,28 +1462,30 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Noble Vow (IRE)</t>
+          <t>Queen Sana</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K18" t="n">
-        <v>75</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M18" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>62.1</v>
+        <v>43.4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1530,11 +1522,11 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Queen Sana</t>
+          <t>Princess Of Limnos</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1544,16 +1536,16 @@
         <v>127</v>
       </c>
       <c r="K19" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="M19" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>43.4</v>
+        <v>11.7</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1590,34 +1582,34 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Princess Of Limnos</t>
+          <t>In The City</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L20" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M20" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>11.7</v>
+        <v>-26</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1649,40 +1641,24 @@
       <c r="F21" t="n">
         <v>4</v>
       </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>In The City</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>142</v>
-      </c>
-      <c r="K21" t="n">
-        <v>75</v>
-      </c>
-      <c r="L21" t="n">
-        <v>28</v>
-      </c>
-      <c r="M21" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-26</v>
-      </c>
+          <t>Far From Fern</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1839,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K24" t="n">
         <v>51</v>
@@ -1851,7 +1827,7 @@
         <v>148.96</v>
       </c>
       <c r="N24" t="n">
-        <v>53.7</v>
+        <v>51</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1948,34 +1924,36 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Premier (FR)</t>
+          <t>Party Island (IRE)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K26" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>129.12</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>64.40000000000001</v>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -2004,28 +1982,30 @@
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Party Island (IRE)</t>
+          <t>Galaxy Wonder (IRE)</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K27" t="n">
-        <v>67</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M27" t="n">
         <v>129.12</v>
       </c>
       <c r="N27" t="n">
-        <v>64.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2033,7 +2013,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2062,30 +2042,30 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Galaxy Wonder (IRE)</t>
+          <t>Prodigal Son</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K28" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="M28" t="n">
         <v>129.12</v>
       </c>
       <c r="N28" t="n">
-        <v>66.3</v>
+        <v>63.6</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2093,7 +2073,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -2122,30 +2102,30 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Prodigal Son</t>
+          <t>Criminal</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K29" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>129.12</v>
       </c>
       <c r="N29" t="n">
-        <v>63.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2153,7 +2133,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2181,40 +2161,24 @@
       <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Criminal</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>134</v>
-      </c>
-      <c r="K30" t="n">
-        <v>71</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>129.12</v>
-      </c>
-      <c r="N30" t="n">
-        <v>64.09999999999999</v>
-      </c>
+          <t>Premier (FR)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2491,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K35" t="n">
         <v>59</v>
@@ -2503,7 +2467,7 @@
         <v>100.74</v>
       </c>
       <c r="N35" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2840,11 +2804,11 @@
         <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Food For Thought</t>
+          <t>Lovers Leap (IRE)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2854,20 +2818,22 @@
         <v>128</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>94.69</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>58.1</v>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2896,11 +2862,11 @@
         <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Lovers Leap (IRE)</t>
+          <t>Talking In Kode</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2910,14 +2876,16 @@
         <v>128</v>
       </c>
       <c r="K42" t="n">
-        <v>71</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M42" t="n">
         <v>94.69</v>
       </c>
       <c r="N42" t="n">
-        <v>58.1</v>
+        <v>43</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2954,11 +2922,11 @@
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Talking In Kode</t>
+          <t>Longevity (IRE)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2971,13 +2939,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="M43" t="n">
         <v>94.69</v>
       </c>
       <c r="N43" t="n">
-        <v>43</v>
+        <v>21.6</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3014,11 +2982,11 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Longevity (IRE)</t>
+          <t>Crown Of Dreams</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3031,13 +2999,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="M44" t="n">
         <v>94.69</v>
       </c>
       <c r="N44" t="n">
-        <v>21.6</v>
+        <v>-0.1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3045,7 +3013,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
@@ -3074,30 +3042,30 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Crown Of Dreams</t>
+          <t>Way Of The Will (USA)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>17.5</v>
+        <v>18.75</v>
       </c>
       <c r="M45" t="n">
         <v>94.69</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.1</v>
+        <v>6.8</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3105,7 +3073,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3133,40 +3101,24 @@
       <c r="F46" t="n">
         <v>4</v>
       </c>
-      <c r="G46" t="n">
-        <v>5</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Way Of The Will (USA)</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" t="n">
-        <v>140</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="M46" t="n">
-        <v>94.69</v>
-      </c>
-      <c r="N46" t="n">
-        <v>6.8</v>
-      </c>
+          <t>Food For Thought</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3850,34 +3802,36 @@
         <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Beerwah (IRE)</t>
+          <t>Dandy Dinmont (IRE)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K58" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>63.5</v>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>72.09999999999999</v>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
@@ -3906,28 +3860,30 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Dandy Dinmont (IRE)</t>
+          <t>Jojo Rabbit</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K59" t="n">
-        <v>62</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M59" t="n">
         <v>63.5</v>
       </c>
       <c r="N59" t="n">
-        <v>72.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3935,7 +3891,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3964,30 +3920,30 @@
         <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Jojo Rabbit</t>
+          <t>Miss Brazen</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K60" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M60" t="n">
         <v>63.5</v>
       </c>
       <c r="N60" t="n">
-        <v>73.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4024,30 +3980,30 @@
         <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Miss Brazen</t>
+          <t>Sherlock (IRE)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K61" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M61" t="n">
         <v>63.5</v>
       </c>
       <c r="N61" t="n">
-        <v>74.8</v>
+        <v>66.5</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4055,7 +4011,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4084,30 +4040,30 @@
         <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sherlock (IRE)</t>
+          <t>Glory Hyde (IRE)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K62" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L62" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="M62" t="n">
         <v>63.5</v>
       </c>
       <c r="N62" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4144,30 +4100,30 @@
         <v>5</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Glory Hyde (IRE)</t>
+          <t>Dark Kestrel (IRE)</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K63" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L63" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="M63" t="n">
         <v>63.5</v>
       </c>
       <c r="N63" t="n">
-        <v>66.40000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4175,7 +4131,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
@@ -4204,30 +4160,30 @@
         <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Dark Kestrel (IRE)</t>
+          <t>Without Flaw (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K64" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="M64" t="n">
         <v>63.5</v>
       </c>
       <c r="N64" t="n">
-        <v>57.3</v>
+        <v>49.5</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4235,7 +4191,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
@@ -4264,30 +4220,30 @@
         <v>5</v>
       </c>
       <c r="G65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Without Flaw (IRE)</t>
+          <t>Fuji Mountain (IRE)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K65" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L65" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M65" t="n">
         <v>63.5</v>
       </c>
       <c r="N65" t="n">
-        <v>51.2</v>
+        <v>58.2</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4295,7 +4251,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4324,30 +4280,30 @@
         <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fuji Mountain (IRE)</t>
+          <t>Tanjen (IRE)</t>
         </is>
       </c>
       <c r="I66" t="n">
         <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L66" t="n">
-        <v>4.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="M66" t="n">
         <v>63.5</v>
       </c>
       <c r="N66" t="n">
-        <v>59.5</v>
+        <v>55</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4355,7 +4311,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4384,30 +4340,30 @@
         <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tanjen (IRE)</t>
+          <t>Hover On The Wind (IRE)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K67" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L67" t="n">
-        <v>5.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M67" t="n">
         <v>63.5</v>
       </c>
       <c r="N67" t="n">
-        <v>55</v>
+        <v>46.9</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4415,7 +4371,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4443,40 +4399,24 @@
       <c r="F68" t="n">
         <v>5</v>
       </c>
-      <c r="G68" t="n">
-        <v>10</v>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Hover On The Wind (IRE)</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>135</v>
-      </c>
-      <c r="K68" t="n">
-        <v>70</v>
-      </c>
-      <c r="L68" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M68" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="N68" t="n">
-        <v>46.9</v>
-      </c>
+          <t>Beerwah (IRE)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4633,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K71" t="n">
         <v>64</v>
@@ -4645,7 +4585,7 @@
         <v>106.76</v>
       </c>
       <c r="N71" t="n">
-        <v>69.7</v>
+        <v>67.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4933,7 +4873,7 @@
         <v>6</v>
       </c>
       <c r="J76" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K76" t="n">
         <v>63</v>
@@ -4945,7 +4885,7 @@
         <v>106.76</v>
       </c>
       <c r="N76" t="n">
-        <v>60.6</v>
+        <v>56.5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4953,7 +4893,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="77">
@@ -5119,7 +5059,7 @@
         <v>62</v>
       </c>
       <c r="L79" t="n">
-        <v>7.05</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="M79" t="n">
         <v>106.76</v>
@@ -5133,7 +5073,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -5179,7 +5119,7 @@
         <v>62</v>
       </c>
       <c r="L80" t="n">
-        <v>7.08</v>
+        <v>7.080000000000001</v>
       </c>
       <c r="M80" t="n">
         <v>106.76</v>
@@ -5193,7 +5133,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5818,11 +5758,11 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Chamonix (IRE)</t>
+          <t>Alphonsus Liguori</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5838,14 +5778,16 @@
       <c r="M91" t="n">
         <v>103.48</v>
       </c>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>78.5</v>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5872,11 +5814,11 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Connor Of Mali (IRE)</t>
+          <t>Res Ipsa</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5888,18 +5830,22 @@
       <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M92" t="n">
         <v>103.48</v>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>77.3</v>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5926,11 +5872,11 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Vico Road (IRE)</t>
+          <t>Oro Blanco (IRE)</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5942,18 +5888,22 @@
       <c r="K93" t="n">
         <v>0</v>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M93" t="n">
         <v>103.48</v>
       </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>70.8</v>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5980,11 +5930,11 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Alphonsus Liguori</t>
+          <t>Mergus Serrator (IRE)</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5996,12 +5946,14 @@
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>3.6</v>
+      </c>
       <c r="M94" t="n">
         <v>103.48</v>
       </c>
       <c r="N94" t="n">
-        <v>78.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6036,11 +5988,11 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Res Ipsa</t>
+          <t>Lonely Island (FR)</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -6053,13 +6005,13 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="M95" t="n">
         <v>103.48</v>
       </c>
       <c r="N95" t="n">
-        <v>77.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6094,11 +6046,11 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Oro Blanco (IRE)</t>
+          <t>Dark Leader (IRE)</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -6111,13 +6063,13 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="M96" t="n">
         <v>103.48</v>
       </c>
       <c r="N96" t="n">
-        <v>70.8</v>
+        <v>62.7</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6152,11 +6104,11 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Mergus Serrator (IRE)</t>
+          <t>Henry Hudson</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -6169,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>3.6</v>
+        <v>9.85</v>
       </c>
       <c r="M97" t="n">
         <v>103.48</v>
       </c>
       <c r="N97" t="n">
-        <v>70.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6210,11 +6162,11 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Lonely Island (FR)</t>
+          <t>Second Line (IRE)</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -6227,13 +6179,13 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>4.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M98" t="n">
         <v>103.48</v>
       </c>
       <c r="N98" t="n">
-        <v>69.09999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6268,30 +6220,30 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Dark Leader (IRE)</t>
+          <t>Amrum</t>
         </is>
       </c>
       <c r="I99" t="n">
         <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>5.6</v>
+        <v>10.95</v>
       </c>
       <c r="M99" t="n">
         <v>103.48</v>
       </c>
       <c r="N99" t="n">
-        <v>62.7</v>
+        <v>43.2</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6325,40 +6277,24 @@
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>7</v>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Henry Hudson</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" t="n">
-        <v>134</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="M100" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="N100" t="n">
-        <v>56.2</v>
-      </c>
+          <t>Connor Of Mali (IRE)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6383,40 +6319,24 @@
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="n">
-        <v>8</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Second Line (IRE)</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" t="n">
-        <v>134</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="M101" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="N101" t="n">
-        <v>55.1</v>
-      </c>
+          <t>Vico Road (IRE)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6441,40 +6361,24 @@
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="n">
-        <v>9</v>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Amrum</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" t="n">
-        <v>134</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="M102" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="N102" t="n">
-        <v>48.4</v>
-      </c>
+          <t>Chamonix (IRE)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6683,7 +6587,7 @@
         <v>3</v>
       </c>
       <c r="J106" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K106" t="n">
         <v>76</v>
@@ -6695,7 +6599,7 @@
         <v>105.69</v>
       </c>
       <c r="N106" t="n">
-        <v>37.3</v>
+        <v>31.2</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6703,7 +6607,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="107">
@@ -6819,7 +6723,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -7598,34 +7502,36 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Ethelwulf</t>
+          <t>Nibras Rainbow (IRE)</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K122" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
         <v>103.9</v>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>60.7</v>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>-17</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="123">
@@ -7652,34 +7558,38 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Morning Approach (IRE)</t>
+          <t>Jasmine Affanalis (IRE)</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K123" t="n">
-        <v>55</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.05</v>
+      </c>
       <c r="M123" t="n">
         <v>103.9</v>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>73.90000000000001</v>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>-17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -7706,34 +7616,38 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Hot To Foxtrot (IRE)</t>
+          <t>Secret Magician (IRE)</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K124" t="n">
-        <v>55</v>
-      </c>
-      <c r="L124" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M124" t="n">
         <v>103.9</v>
       </c>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>61.6</v>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>-17</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="125">
@@ -7760,28 +7674,30 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nibras Rainbow (IRE)</t>
+          <t>Toy Soldier (IRE)</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K125" t="n">
-        <v>46</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1.7</v>
+      </c>
       <c r="M125" t="n">
         <v>103.9</v>
       </c>
       <c r="N125" t="n">
-        <v>60.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -7789,7 +7705,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -7816,30 +7732,30 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Jasmine Affanalis (IRE)</t>
+          <t>Saith Seren</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="K126" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L126" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="M126" t="n">
         <v>103.9</v>
       </c>
       <c r="N126" t="n">
-        <v>73.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -7847,7 +7763,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="127">
@@ -7874,30 +7790,30 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Secret Magician (IRE)</t>
+          <t>Tero Drosa (IRE)</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J127" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K127" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="L127" t="n">
-        <v>0.2</v>
+        <v>2.55</v>
       </c>
       <c r="M127" t="n">
         <v>103.9</v>
       </c>
       <c r="N127" t="n">
-        <v>67.3</v>
+        <v>70.3</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -7905,7 +7821,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -7932,30 +7848,30 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Toy Soldier (IRE)</t>
+          <t>Hale Bopp (IRE)</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J128" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="K128" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="L128" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="M128" t="n">
         <v>103.9</v>
       </c>
       <c r="N128" t="n">
-        <v>64.40000000000001</v>
+        <v>41.4</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -7963,7 +7879,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="129">
@@ -7990,30 +7906,30 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Saith Seren</t>
+          <t>Can I Kiss You (IRE)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K129" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L129" t="n">
-        <v>1.8</v>
+        <v>4.55</v>
       </c>
       <c r="M129" t="n">
         <v>103.9</v>
       </c>
       <c r="N129" t="n">
-        <v>58.4</v>
+        <v>56.7</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -8021,7 +7937,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -8048,30 +7964,30 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tero Drosa (IRE)</t>
+          <t>Friars Gate (IRE)</t>
         </is>
       </c>
       <c r="I130" t="n">
         <v>4</v>
       </c>
       <c r="J130" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="K130" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L130" t="n">
-        <v>2.55</v>
+        <v>6.55</v>
       </c>
       <c r="M130" t="n">
         <v>103.9</v>
       </c>
       <c r="N130" t="n">
-        <v>70.3</v>
+        <v>51.2</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -8079,7 +7995,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8106,30 +8022,30 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Hale Bopp (IRE)</t>
+          <t>Tynamite (IRE)</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J131" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="K131" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L131" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M131" t="n">
         <v>103.9</v>
       </c>
       <c r="N131" t="n">
-        <v>45.7</v>
+        <v>24.6</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8137,7 +8053,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="132">
@@ -8164,30 +8080,30 @@
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Can I Kiss You (IRE)</t>
+          <t>Chipsrdown (IRE)</t>
         </is>
       </c>
       <c r="I132" t="n">
         <v>4</v>
       </c>
       <c r="J132" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K132" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L132" t="n">
-        <v>4.55</v>
+        <v>8.85</v>
       </c>
       <c r="M132" t="n">
         <v>103.9</v>
       </c>
       <c r="N132" t="n">
-        <v>56.7</v>
+        <v>51.5</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8195,7 +8111,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -8222,30 +8138,30 @@
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Friars Gate (IRE)</t>
+          <t>Lorrs Girl (IRE)</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K133" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L133" t="n">
-        <v>6.55</v>
+        <v>9.35</v>
       </c>
       <c r="M133" t="n">
         <v>103.9</v>
       </c>
       <c r="N133" t="n">
-        <v>55.6</v>
+        <v>37.4</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -8253,7 +8169,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -8280,30 +8196,30 @@
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Tynamite (IRE)</t>
+          <t>Mogwli (IRE)</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J134" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K134" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L134" t="n">
-        <v>8.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M134" t="n">
         <v>103.9</v>
       </c>
       <c r="N134" t="n">
-        <v>32.5</v>
+        <v>36.6</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -8311,7 +8227,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8338,30 +8254,30 @@
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Chipsrdown (IRE)</t>
+          <t>Peig Sayers (IRE)</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K135" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L135" t="n">
-        <v>8.85</v>
+        <v>11.45</v>
       </c>
       <c r="M135" t="n">
         <v>103.9</v>
       </c>
       <c r="N135" t="n">
-        <v>51.5</v>
+        <v>41.7</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -8369,7 +8285,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -8396,30 +8312,30 @@
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lorrs Girl (IRE)</t>
+          <t>Swiss Army Officer (IRE)</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J136" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="K136" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L136" t="n">
-        <v>9.35</v>
+        <v>13.7</v>
       </c>
       <c r="M136" t="n">
         <v>103.9</v>
       </c>
       <c r="N136" t="n">
-        <v>37.4</v>
+        <v>10.6</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -8427,7 +8343,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8453,40 +8369,24 @@
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="n">
-        <v>13</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Mogwli (IRE)</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>9</v>
-      </c>
-      <c r="J137" t="n">
-        <v>134</v>
-      </c>
-      <c r="K137" t="n">
-        <v>52</v>
-      </c>
-      <c r="L137" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="M137" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="N137" t="n">
-        <v>43.3</v>
-      </c>
+          <t>Ethelwulf</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P137" t="n">
-        <v>2</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8511,40 +8411,24 @@
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="n">
-        <v>14</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Peig Sayers (IRE)</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>5</v>
-      </c>
-      <c r="J138" t="n">
-        <v>139</v>
-      </c>
-      <c r="K138" t="n">
-        <v>57</v>
-      </c>
-      <c r="L138" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="M138" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="N138" t="n">
-        <v>41.7</v>
-      </c>
+          <t>Hot To Foxtrot (IRE)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P138" t="n">
-        <v>2</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8569,40 +8453,24 @@
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="n">
-        <v>15</v>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Swiss Army Officer (IRE)</t>
-        </is>
-      </c>
-      <c r="I139" t="n">
-        <v>11</v>
-      </c>
-      <c r="J139" t="n">
-        <v>122</v>
-      </c>
-      <c r="K139" t="n">
-        <v>39</v>
-      </c>
-      <c r="L139" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M139" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="N139" t="n">
-        <v>18</v>
-      </c>
+          <t>Morning Approach (IRE)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8628,34 +8496,36 @@
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Divine Believer (IRE)</t>
+          <t>Femme Beauty (IRE)</t>
         </is>
       </c>
       <c r="I140" t="n">
         <v>3</v>
       </c>
       <c r="J140" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K140" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
         <v>148.44</v>
       </c>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>63.4</v>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141">
@@ -8682,28 +8552,30 @@
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Femme Beauty (IRE)</t>
+          <t>Musashi (IRE)</t>
         </is>
       </c>
       <c r="I141" t="n">
         <v>3</v>
       </c>
       <c r="J141" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K141" t="n">
-        <v>57</v>
-      </c>
-      <c r="L141" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M141" t="n">
         <v>148.44</v>
       </c>
       <c r="N141" t="n">
-        <v>63.4</v>
+        <v>70.2</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8711,7 +8583,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>-5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
@@ -8738,30 +8610,30 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Musashi (IRE)</t>
+          <t>Delusional (IRE)</t>
         </is>
       </c>
       <c r="I142" t="n">
         <v>3</v>
       </c>
       <c r="J142" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K142" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L142" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="M142" t="n">
         <v>148.44</v>
       </c>
       <c r="N142" t="n">
-        <v>70.2</v>
+        <v>67.8</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -8769,7 +8641,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8796,30 +8668,30 @@
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Delusional (IRE)</t>
+          <t>Gatlinburg (IRE)</t>
         </is>
       </c>
       <c r="I143" t="n">
         <v>3</v>
       </c>
       <c r="J143" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K143" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L143" t="n">
-        <v>0.65</v>
+        <v>1.4</v>
       </c>
       <c r="M143" t="n">
         <v>148.44</v>
       </c>
       <c r="N143" t="n">
-        <v>67.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -8854,30 +8726,30 @@
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Gatlinburg (IRE)</t>
+          <t>Chicago Moon (IRE)</t>
         </is>
       </c>
       <c r="I144" t="n">
         <v>3</v>
       </c>
       <c r="J144" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K144" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L144" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M144" t="n">
         <v>148.44</v>
       </c>
       <c r="N144" t="n">
-        <v>67.40000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8885,7 +8757,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="145">
@@ -8912,30 +8784,30 @@
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Chicago Moon (IRE)</t>
+          <t>Honouramongthieves</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>3</v>
       </c>
       <c r="J145" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K145" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="L145" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="M145" t="n">
         <v>148.44</v>
       </c>
       <c r="N145" t="n">
-        <v>63.3</v>
+        <v>70.2</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -8943,7 +8815,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="146">
@@ -8970,30 +8842,30 @@
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Honouramongthieves</t>
+          <t>Blissful Bonita (IRE)</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K146" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L146" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="M146" t="n">
         <v>148.44</v>
       </c>
       <c r="N146" t="n">
-        <v>70.2</v>
+        <v>64.3</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9001,7 +8873,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -9028,30 +8900,30 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Blissful Bonita (IRE)</t>
+          <t>Mount Eden (IRE)</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>3</v>
       </c>
       <c r="J147" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K147" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L147" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="M147" t="n">
         <v>148.44</v>
       </c>
       <c r="N147" t="n">
-        <v>64.3</v>
+        <v>60.8</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9059,7 +8931,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -9086,30 +8958,30 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Mount Eden (IRE)</t>
+          <t>Cameclose (IRE)</t>
         </is>
       </c>
       <c r="I148" t="n">
         <v>3</v>
       </c>
       <c r="J148" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K148" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L148" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="M148" t="n">
         <v>148.44</v>
       </c>
       <c r="N148" t="n">
-        <v>62.8</v>
+        <v>59.6</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9144,30 +9016,30 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Cameclose (IRE)</t>
+          <t>Celestially (IRE)</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K149" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L149" t="n">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="M149" t="n">
         <v>148.44</v>
       </c>
       <c r="N149" t="n">
-        <v>59.6</v>
+        <v>57.1</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -9202,30 +9074,30 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Celestially (IRE)</t>
+          <t>Coolangatta (IRE)</t>
         </is>
       </c>
       <c r="I150" t="n">
         <v>3</v>
       </c>
       <c r="J150" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K150" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L150" t="n">
-        <v>5.55</v>
+        <v>13.05</v>
       </c>
       <c r="M150" t="n">
         <v>148.44</v>
       </c>
       <c r="N150" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -9259,40 +9131,24 @@
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="n">
-        <v>11</v>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Coolangatta (IRE)</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>3</v>
-      </c>
-      <c r="J151" t="n">
-        <v>135</v>
-      </c>
-      <c r="K151" t="n">
-        <v>67</v>
-      </c>
-      <c r="L151" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="M151" t="n">
-        <v>148.44</v>
-      </c>
-      <c r="N151" t="n">
-        <v>45.5</v>
-      </c>
+          <t>Divine Believer (IRE)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9318,34 +9174,36 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Slurricane (IRE)</t>
+          <t>Factual Fact (FR)</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J152" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K152" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
         <v>243.78</v>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -9372,28 +9230,30 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Factual Fact (FR)</t>
+          <t>Harrys Legacy</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J153" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K153" t="n">
-        <v>81</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M153" t="n">
         <v>243.78</v>
       </c>
       <c r="N153" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9401,7 +9261,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
@@ -9428,30 +9288,30 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Harrys Legacy</t>
+          <t>Sequoiaspirit (IRE)</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J154" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K154" t="n">
         <v>71</v>
       </c>
       <c r="L154" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
         <v>243.78</v>
       </c>
       <c r="N154" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9459,7 +9319,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="155">
@@ -9486,30 +9346,30 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Sequoiaspirit (IRE)</t>
+          <t>Dark Note</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J155" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K155" t="n">
         <v>71</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="M155" t="n">
         <v>243.78</v>
       </c>
       <c r="N155" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -9517,7 +9377,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -9544,30 +9404,30 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Dark Note</t>
+          <t>Winning Smut (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
         <v>7</v>
       </c>
       <c r="J156" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K156" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L156" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M156" t="n">
         <v>243.78</v>
       </c>
       <c r="N156" t="n">
-        <v>2.3</v>
+        <v>-0.8</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9575,7 +9435,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9602,30 +9462,30 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Winning Smut (IRE)</t>
+          <t>Hidalgo Des Mottes (FR)</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J157" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K157" t="n">
         <v>67</v>
       </c>
       <c r="L157" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="M157" t="n">
         <v>243.78</v>
       </c>
       <c r="N157" t="n">
-        <v>-0.8</v>
+        <v>-24.8</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9633,7 +9493,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="158">
@@ -9660,30 +9520,30 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Hidalgo Des Mottes (FR)</t>
+          <t>Riyami (IRE)</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J158" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K158" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L158" t="n">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
       <c r="M158" t="n">
         <v>243.78</v>
       </c>
       <c r="N158" t="n">
-        <v>-12.2</v>
+        <v>-7.4</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9691,7 +9551,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9718,11 +9578,11 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Riyami (IRE)</t>
+          <t>Wandering Rocks</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -9735,13 +9595,13 @@
         <v>75</v>
       </c>
       <c r="L159" t="n">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="M159" t="n">
         <v>243.78</v>
       </c>
       <c r="N159" t="n">
-        <v>1.3</v>
+        <v>-5.1</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -9776,30 +9636,30 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Wandering Rocks</t>
+          <t>Chain Of Destiny (IRE)</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>7</v>
       </c>
       <c r="J160" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="K160" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="L160" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M160" t="n">
         <v>243.78</v>
       </c>
       <c r="N160" t="n">
-        <v>-5.1</v>
+        <v>-39</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -9807,7 +9667,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -9833,40 +9693,24 @@
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="n">
-        <v>9</v>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Chain Of Destiny (IRE)</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>147</v>
-      </c>
-      <c r="K161" t="n">
-        <v>52</v>
-      </c>
-      <c r="L161" t="n">
-        <v>17</v>
-      </c>
-      <c r="M161" t="n">
-        <v>243.78</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-58.8</v>
-      </c>
+          <t>Slurricane (IRE)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9892,34 +9736,36 @@
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Farren Glory (IRE)</t>
+          <t>Kizlyar (IRE)</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
         <v>192.08</v>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>80.8</v>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -9946,15 +9792,15 @@
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Kizlyar (IRE)</t>
+          <t>Sky Captain (IRE)</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>138</v>
@@ -9962,12 +9808,14 @@
       <c r="K163" t="n">
         <v>92</v>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M163" t="n">
         <v>192.08</v>
       </c>
       <c r="N163" t="n">
-        <v>80.8</v>
+        <v>78</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10002,11 +9850,11 @@
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sky Captain (IRE)</t>
+          <t>Tim Toe (IRE)</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -10016,16 +9864,16 @@
         <v>138</v>
       </c>
       <c r="K164" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="M164" t="n">
         <v>192.08</v>
       </c>
       <c r="N164" t="n">
-        <v>78</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10060,30 +9908,30 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tim Toe (IRE)</t>
+          <t>Defiantly (FR)</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J165" t="n">
         <v>138</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L165" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="M165" t="n">
         <v>192.08</v>
       </c>
       <c r="N165" t="n">
-        <v>77.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10118,30 +9966,30 @@
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Defiantly (FR)</t>
+          <t>Stellar Quality (IRE)</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>4</v>
       </c>
       <c r="J166" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K166" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="L166" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="M166" t="n">
         <v>192.08</v>
       </c>
       <c r="N166" t="n">
-        <v>74.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10176,30 +10024,30 @@
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Stellar Quality (IRE)</t>
+          <t>Ebony King (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K167" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="M167" t="n">
         <v>192.08</v>
       </c>
       <c r="N167" t="n">
-        <v>66.3</v>
+        <v>63.3</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10233,40 +10081,24 @@
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="n">
-        <v>6</v>
-      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Ebony King (IRE)</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>5</v>
-      </c>
-      <c r="J168" t="n">
-        <v>130</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M168" t="n">
-        <v>192.08</v>
-      </c>
-      <c r="N168" t="n">
-        <v>63.3</v>
-      </c>
+          <t>Farren Glory (IRE)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10363,7 +10195,7 @@
         <v>6</v>
       </c>
       <c r="J170" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K170" t="n">
         <v>72</v>
@@ -10375,7 +10207,7 @@
         <v>218.8</v>
       </c>
       <c r="N170" t="n">
-        <v>-67</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -10383,7 +10215,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10423,7 +10255,7 @@
         <v>8</v>
       </c>
       <c r="J171" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K171" t="n">
         <v>74</v>
@@ -10435,7 +10267,7 @@
         <v>218.8</v>
       </c>
       <c r="N171" t="n">
-        <v>-66.90000000000001</v>
+        <v>-89.2</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10443,7 +10275,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10483,7 +10315,7 @@
         <v>9</v>
       </c>
       <c r="J172" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K172" t="n">
         <v>64</v>
@@ -10495,7 +10327,7 @@
         <v>218.8</v>
       </c>
       <c r="N172" t="n">
-        <v>-99.5</v>
+        <v>-121.3</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -10503,7 +10335,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="173">
@@ -10543,7 +10375,7 @@
         <v>6</v>
       </c>
       <c r="J173" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K173" t="n">
         <v>70</v>
@@ -10555,7 +10387,7 @@
         <v>218.8</v>
       </c>
       <c r="N173" t="n">
-        <v>-106.8</v>
+        <v>-111</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10563,7 +10395,7 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -10603,7 +10435,7 @@
         <v>4</v>
       </c>
       <c r="J174" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K174" t="n">
         <v>69</v>
@@ -10615,7 +10447,7 @@
         <v>218.8</v>
       </c>
       <c r="N174" t="n">
-        <v>-117.6</v>
+        <v>-117.1</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10623,7 +10455,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -11261,7 +11093,7 @@
         <v>3</v>
       </c>
       <c r="J185" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -11273,7 +11105,7 @@
         <v>99.58</v>
       </c>
       <c r="N185" t="n">
-        <v>-7.8</v>
+        <v>-13.5</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -11685,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>6.95</v>
+        <v>6.949999999999999</v>
       </c>
       <c r="M192" t="n">
         <v>85.28</v>
@@ -12277,7 +12109,7 @@
         <v>3</v>
       </c>
       <c r="J202" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K202" t="n">
         <v>52</v>
@@ -12289,7 +12121,7 @@
         <v>86.04000000000001</v>
       </c>
       <c r="N202" t="n">
-        <v>21.4</v>
+        <v>18.2</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -12337,7 +12169,7 @@
         <v>3</v>
       </c>
       <c r="J203" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K203" t="n">
         <v>61</v>
@@ -12349,7 +12181,7 @@
         <v>86.04000000000001</v>
       </c>
       <c r="N203" t="n">
-        <v>7.9</v>
+        <v>4.6</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -12386,34 +12218,36 @@
         <v>4</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Dontspoilasale (IRE)</t>
+          <t>Zatsgood</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J204" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K204" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="n">
+        <v>84.59999999999999</v>
+      </c>
       <c r="O204" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P204" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -12442,28 +12276,30 @@
         <v>4</v>
       </c>
       <c r="G205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Zatsgood</t>
+          <t>Zoffandia (IRE)</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J205" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K205" t="n">
-        <v>78</v>
-      </c>
-      <c r="L205" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M205" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N205" t="n">
-        <v>84.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -12500,30 +12336,30 @@
         <v>4</v>
       </c>
       <c r="G206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Zoffandia (IRE)</t>
+          <t>Signcastle City (IRE)</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J206" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="K206" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L206" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="M206" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N206" t="n">
-        <v>78.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -12531,7 +12367,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="207">
@@ -12560,30 +12396,30 @@
         <v>4</v>
       </c>
       <c r="G207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Signcastle City (IRE)</t>
+          <t>Metallo (IRE)</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J207" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K207" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L207" t="n">
-        <v>3</v>
+        <v>7.25</v>
       </c>
       <c r="M207" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N207" t="n">
-        <v>72</v>
+        <v>66.2</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -12591,7 +12427,7 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -12620,30 +12456,30 @@
         <v>4</v>
       </c>
       <c r="G208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Metallo (IRE)</t>
+          <t>Studious (IRE)</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J208" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K208" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L208" t="n">
-        <v>7.25</v>
+        <v>9.5</v>
       </c>
       <c r="M208" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N208" t="n">
-        <v>66.2</v>
+        <v>60.1</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -12680,30 +12516,30 @@
         <v>4</v>
       </c>
       <c r="G209" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Studious (IRE)</t>
+          <t>Buy The Dip</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J209" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K209" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="L209" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="M209" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N209" t="n">
-        <v>60.1</v>
+        <v>45</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -12740,34 +12576,34 @@
         <v>4</v>
       </c>
       <c r="G210" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Buy The Dip</t>
+          <t>Frostmagic (IRE)</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J210" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K210" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="L210" t="n">
-        <v>10.5</v>
+        <v>29.5</v>
       </c>
       <c r="M210" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N210" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -12800,30 +12636,30 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Frostmagic (IRE)</t>
+          <t>Special Ghaiyyath (IRE)</t>
         </is>
       </c>
       <c r="I211" t="n">
         <v>4</v>
       </c>
       <c r="J211" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K211" t="n">
         <v>78</v>
       </c>
       <c r="L211" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="M211" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N211" t="n">
-        <v>26.1</v>
+        <v>21.1</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -12860,30 +12696,30 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Special Ghaiyyath (IRE)</t>
+          <t>Baltic Voyage</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J212" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K212" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L212" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M212" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="N212" t="n">
-        <v>25.5</v>
+        <v>6.3</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -12919,40 +12755,24 @@
       <c r="F213" t="n">
         <v>4</v>
       </c>
-      <c r="G213" t="n">
-        <v>9</v>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Baltic Voyage</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
-        <v>6</v>
-      </c>
-      <c r="J213" t="n">
-        <v>134</v>
-      </c>
-      <c r="K213" t="n">
-        <v>79</v>
-      </c>
-      <c r="L213" t="n">
-        <v>44</v>
-      </c>
-      <c r="M213" t="n">
-        <v>96.93000000000001</v>
-      </c>
-      <c r="N213" t="n">
-        <v>6.3</v>
-      </c>
+          <t>Dontspoilasale (IRE)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12980,34 +12800,36 @@
         <v>4</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Ghisa (IRE)</t>
+          <t>Handle With Care</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J214" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K214" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="n">
         <v>84.77</v>
       </c>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" t="n">
+        <v>68</v>
+      </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P214" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -13036,34 +12858,38 @@
         <v>4</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Moonlight Mirage</t>
+          <t>Brisk Symphony (IRE)</t>
         </is>
       </c>
       <c r="I215" t="n">
         <v>3</v>
       </c>
       <c r="J215" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K215" t="n">
-        <v>77</v>
-      </c>
-      <c r="L215" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M215" t="n">
         <v>84.77</v>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P215" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="216">
@@ -13092,34 +12918,38 @@
         <v>4</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bami (IRE)</t>
+          <t>Barefoot Beach (IRE)</t>
         </is>
       </c>
       <c r="I216" t="n">
         <v>3</v>
       </c>
       <c r="J216" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K216" t="n">
-        <v>70</v>
-      </c>
-      <c r="L216" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M216" t="n">
         <v>84.77</v>
       </c>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="n">
+        <v>63.9</v>
+      </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="217">
@@ -13148,28 +12978,30 @@
         <v>4</v>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Handle With Care</t>
+          <t>Inside Story (IRE)</t>
         </is>
       </c>
       <c r="I217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J217" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K217" t="n">
-        <v>72</v>
-      </c>
-      <c r="L217" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L217" t="n">
+        <v>2.65</v>
+      </c>
       <c r="M217" t="n">
         <v>84.77</v>
       </c>
       <c r="N217" t="n">
-        <v>68</v>
+        <v>62.3</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -13177,7 +13009,7 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="218">
@@ -13206,30 +13038,30 @@
         <v>4</v>
       </c>
       <c r="G218" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Brisk Symphony (IRE)</t>
+          <t>The Third Star</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J218" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K218" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L218" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="M218" t="n">
         <v>84.77</v>
       </c>
       <c r="N218" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -13237,7 +13069,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -13266,30 +13098,30 @@
         <v>4</v>
       </c>
       <c r="G219" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Barefoot Beach (IRE)</t>
+          <t>Bella Bisbee</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J219" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K219" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="L219" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="M219" t="n">
         <v>84.77</v>
       </c>
       <c r="N219" t="n">
-        <v>63.9</v>
+        <v>49.1</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -13297,7 +13129,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="220">
@@ -13326,30 +13158,30 @@
         <v>4</v>
       </c>
       <c r="G220" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Inside Story (IRE)</t>
+          <t>Queue Dos</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J220" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K220" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L220" t="n">
-        <v>2.65</v>
+        <v>6.75</v>
       </c>
       <c r="M220" t="n">
         <v>84.77</v>
       </c>
       <c r="N220" t="n">
-        <v>62.3</v>
+        <v>53.4</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -13357,7 +13189,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -13386,30 +13218,30 @@
         <v>4</v>
       </c>
       <c r="G221" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>The Third Star</t>
+          <t>Bela Sonata</t>
         </is>
       </c>
       <c r="I221" t="n">
         <v>4</v>
       </c>
       <c r="J221" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K221" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L221" t="n">
-        <v>2.75</v>
+        <v>6.8</v>
       </c>
       <c r="M221" t="n">
         <v>84.77</v>
       </c>
       <c r="N221" t="n">
-        <v>66</v>
+        <v>57.2</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -13417,7 +13249,7 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -13446,30 +13278,30 @@
         <v>4</v>
       </c>
       <c r="G222" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bella Bisbee</t>
+          <t>Cloudbuster</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J222" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K222" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L222" t="n">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M222" t="n">
         <v>84.77</v>
       </c>
       <c r="N222" t="n">
-        <v>49.1</v>
+        <v>36.2</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -13477,7 +13309,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -13505,40 +13337,24 @@
       <c r="F223" t="n">
         <v>4</v>
       </c>
-      <c r="G223" t="n">
-        <v>7</v>
-      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Queue Dos</t>
-        </is>
-      </c>
-      <c r="I223" t="n">
-        <v>4</v>
-      </c>
-      <c r="J223" t="n">
-        <v>135</v>
-      </c>
-      <c r="K223" t="n">
-        <v>78</v>
-      </c>
-      <c r="L223" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="M223" t="n">
-        <v>84.77</v>
-      </c>
-      <c r="N223" t="n">
-        <v>53.4</v>
-      </c>
+          <t>Ghisa (IRE)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13565,40 +13381,24 @@
       <c r="F224" t="n">
         <v>4</v>
       </c>
-      <c r="G224" t="n">
-        <v>8</v>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bela Sonata</t>
-        </is>
-      </c>
-      <c r="I224" t="n">
-        <v>4</v>
-      </c>
-      <c r="J224" t="n">
-        <v>142</v>
-      </c>
-      <c r="K224" t="n">
-        <v>85</v>
-      </c>
-      <c r="L224" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M224" t="n">
-        <v>84.77</v>
-      </c>
-      <c r="N224" t="n">
-        <v>57.2</v>
-      </c>
+          <t>Moonlight Mirage</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P224" t="n">
-        <v>2</v>
-      </c>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13625,40 +13425,24 @@
       <c r="F225" t="n">
         <v>4</v>
       </c>
-      <c r="G225" t="n">
-        <v>9</v>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Cloudbuster</t>
-        </is>
-      </c>
-      <c r="I225" t="n">
-        <v>3</v>
-      </c>
-      <c r="J225" t="n">
-        <v>121</v>
-      </c>
-      <c r="K225" t="n">
-        <v>76</v>
-      </c>
-      <c r="L225" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M225" t="n">
-        <v>84.77</v>
-      </c>
-      <c r="N225" t="n">
-        <v>38.3</v>
-      </c>
+          <t>Bami (IRE)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P225" t="n">
-        <v>0</v>
-      </c>
+      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13686,34 +13470,36 @@
         <v>4</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Arths Gold</t>
+          <t>Yaa Min</t>
         </is>
       </c>
       <c r="I226" t="n">
         <v>4</v>
       </c>
       <c r="J226" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K226" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="n">
         <v>154.56</v>
       </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="n">
+        <v>44.2</v>
+      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="227">
@@ -13742,28 +13528,30 @@
         <v>4</v>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Yaa Min</t>
+          <t>Penzance</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J227" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K227" t="n">
-        <v>77</v>
-      </c>
-      <c r="L227" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M227" t="n">
         <v>154.56</v>
       </c>
       <c r="N227" t="n">
-        <v>47.4</v>
+        <v>51.5</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -13771,7 +13559,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -13800,30 +13588,30 @@
         <v>4</v>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Penzance</t>
+          <t>Epictetus (IRE)</t>
         </is>
       </c>
       <c r="I228" t="n">
         <v>6</v>
       </c>
       <c r="J228" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K228" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L228" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="M228" t="n">
         <v>154.56</v>
       </c>
       <c r="N228" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -13860,30 +13648,30 @@
         <v>4</v>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Epictetus (IRE)</t>
+          <t>Lightning Tiger (IRE)</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K229" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L229" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="M229" t="n">
         <v>154.56</v>
       </c>
       <c r="N229" t="n">
-        <v>51.1</v>
+        <v>46.8</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -13920,30 +13708,30 @@
         <v>4</v>
       </c>
       <c r="G230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lightning Tiger (IRE)</t>
+          <t>Victors Spirit (SAF)</t>
         </is>
       </c>
       <c r="I230" t="n">
         <v>4</v>
       </c>
       <c r="J230" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K230" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L230" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="M230" t="n">
         <v>154.56</v>
       </c>
       <c r="N230" t="n">
-        <v>46.8</v>
+        <v>42.1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -13980,30 +13768,30 @@
         <v>4</v>
       </c>
       <c r="G231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Victors Spirit (SAF)</t>
+          <t>Twilight Moon</t>
         </is>
       </c>
       <c r="I231" t="n">
         <v>4</v>
       </c>
       <c r="J231" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K231" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L231" t="n">
-        <v>1.55</v>
+        <v>4.3</v>
       </c>
       <c r="M231" t="n">
         <v>154.56</v>
       </c>
       <c r="N231" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -14040,30 +13828,30 @@
         <v>4</v>
       </c>
       <c r="G232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Twilight Moon</t>
+          <t>Rogue Impact</t>
         </is>
       </c>
       <c r="I232" t="n">
         <v>4</v>
       </c>
       <c r="J232" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K232" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L232" t="n">
-        <v>4.3</v>
+        <v>10.3</v>
       </c>
       <c r="M232" t="n">
         <v>154.56</v>
       </c>
       <c r="N232" t="n">
-        <v>40.6</v>
+        <v>30</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -14099,40 +13887,24 @@
       <c r="F233" t="n">
         <v>4</v>
       </c>
-      <c r="G233" t="n">
-        <v>7</v>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Rogue Impact</t>
-        </is>
-      </c>
-      <c r="I233" t="n">
-        <v>4</v>
-      </c>
-      <c r="J233" t="n">
-        <v>134</v>
-      </c>
-      <c r="K233" t="n">
-        <v>79</v>
-      </c>
-      <c r="L233" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M233" t="n">
-        <v>154.56</v>
-      </c>
-      <c r="N233" t="n">
-        <v>30</v>
-      </c>
+          <t>Arths Gold</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P233" t="n">
-        <v>0</v>
-      </c>
+      <c r="P233" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
